--- a/config/配置_开发机_测试.xlsx
+++ b/config/配置_开发机_测试.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="22010" windowHeight="12332"/>
+    <workbookView windowWidth="18569" windowHeight="11268" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="project" sheetId="1" r:id="rId1"/>
@@ -132,7 +132,7 @@
     <t>north_modbus_conf</t>
   </si>
   <si>
-    <t>./config/MODBUS_REGISTERS.xlsx</t>
+    <t>./config/北向/MODBUS_REGISTERS.xlsx</t>
   </si>
   <si>
     <t>北向Modbus配置文件</t>
